--- a/artfynd/A 50084-2025 artfynd.xlsx
+++ b/artfynd/A 50084-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,409 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129949383</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bollebygd kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>362878</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6394805</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129949593</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58413</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bollebygd kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>362871</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6394809</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129949426</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bollebygd kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>363039</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6394494</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sandra Johansson, Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129949425</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bollebygd kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>363034</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6394565</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sandra Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sandra Johansson, Elin Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50084-2025 artfynd.xlsx
+++ b/artfynd/A 50084-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129949383</v>
       </c>
       <c r="B3" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129949593</v>
       </c>
       <c r="B4" t="n">
-        <v>58413</v>
+        <v>58416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129949426</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>129949425</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50084-2025 artfynd.xlsx
+++ b/artfynd/A 50084-2025 artfynd.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sandra Johansson, Elin Eriksson</t>
+          <t>Elin Eriksson, Sandra Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sandra Johansson, Elin Eriksson</t>
+          <t>Elin Eriksson, Sandra Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 50084-2025 artfynd.xlsx
+++ b/artfynd/A 50084-2025 artfynd.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Eriksson, Sandra Johansson</t>
+          <t>Sandra Johansson, Elin Eriksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Eriksson, Sandra Johansson</t>
+          <t>Sandra Johansson, Elin Eriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 50084-2025 artfynd.xlsx
+++ b/artfynd/A 50084-2025 artfynd.xlsx
@@ -787,50 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129949383</v>
+        <v>129949593</v>
       </c>
       <c r="B3" t="n">
-        <v>57895</v>
+        <v>58419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bollebygd kommun, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>362878</v>
+        <v>362871</v>
       </c>
       <c r="R3" t="n">
-        <v>6394805</v>
+        <v>6394809</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -889,45 +884,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129949593</v>
+        <v>129949383</v>
       </c>
       <c r="B4" t="n">
-        <v>58416</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bollebygd kommun, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>362871</v>
+        <v>362878</v>
       </c>
       <c r="R4" t="n">
-        <v>6394809</v>
+        <v>6394805</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -989,7 +989,7 @@
         <v>129949426</v>
       </c>
       <c r="B5" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>129949425</v>
       </c>
       <c r="B6" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50084-2025 artfynd.xlsx
+++ b/artfynd/A 50084-2025 artfynd.xlsx
@@ -787,45 +787,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129949593</v>
+        <v>129949383</v>
       </c>
       <c r="B3" t="n">
-        <v>58419</v>
+        <v>57898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bollebygd kommun, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>362871</v>
+        <v>362878</v>
       </c>
       <c r="R3" t="n">
-        <v>6394809</v>
+        <v>6394805</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -884,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129949383</v>
+        <v>129949593</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>58419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bollebygd kommun, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>362878</v>
+        <v>362871</v>
       </c>
       <c r="R4" t="n">
-        <v>6394805</v>
+        <v>6394809</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 50084-2025 artfynd.xlsx
+++ b/artfynd/A 50084-2025 artfynd.xlsx
@@ -787,50 +787,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129949383</v>
+        <v>129949593</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>58419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bollebygd kommun, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>362878</v>
+        <v>362871</v>
       </c>
       <c r="R3" t="n">
-        <v>6394805</v>
+        <v>6394809</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -889,45 +884,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129949593</v>
+        <v>129949383</v>
       </c>
       <c r="B4" t="n">
-        <v>58419</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bollebygd kommun, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>362871</v>
+        <v>362878</v>
       </c>
       <c r="R4" t="n">
-        <v>6394809</v>
+        <v>6394805</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>

--- a/artfynd/A 50084-2025 artfynd.xlsx
+++ b/artfynd/A 50084-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129949383</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129949593</v>
       </c>
       <c r="B4" t="n">
-        <v>58419</v>
+        <v>58420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50084-2025 artfynd.xlsx
+++ b/artfynd/A 50084-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129949383</v>
       </c>
       <c r="B3" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129949593</v>
       </c>
       <c r="B4" t="n">
-        <v>58421</v>
+        <v>58506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129949426</v>
       </c>
       <c r="B5" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>129949425</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50084-2025 artfynd.xlsx
+++ b/artfynd/A 50084-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129949383</v>
       </c>
       <c r="B3" t="n">
-        <v>57985</v>
+        <v>57900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129949593</v>
       </c>
       <c r="B4" t="n">
-        <v>58506</v>
+        <v>58421</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129949426</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>129949425</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50084-2025 artfynd.xlsx
+++ b/artfynd/A 50084-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90903850</v>
+        <v>129949425</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Erikshult, Vg</t>
+          <t>Bollebygd kommun, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>363090.8606671396</v>
+        <v>363034</v>
       </c>
       <c r="R2" t="n">
-        <v>6394421.747027134</v>
+        <v>6394565</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-08-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,50 +765,50 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sara Elg</t>
+          <t>Sandra Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Elg</t>
+          <t>Sandra Johansson, Elin Eriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129949383</v>
+        <v>129949426</v>
       </c>
       <c r="B3" t="n">
-        <v>57985</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>362878</v>
+        <v>363039</v>
       </c>
       <c r="R3" t="n">
-        <v>6394805</v>
+        <v>6394494</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -857,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,52 +872,57 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sandra Johansson</t>
+          <t>Sandra Johansson, Elin Eriksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129949593</v>
+        <v>129949383</v>
       </c>
       <c r="B4" t="n">
-        <v>58506</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bollebygd kommun, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>362871</v>
+        <v>362878</v>
       </c>
       <c r="R4" t="n">
-        <v>6394809</v>
+        <v>6394805</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,27 +981,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129949426</v>
+        <v>129949593</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>58636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1015,21 +1010,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bollebygd kommun, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363039</v>
+        <v>362871</v>
       </c>
       <c r="R5" t="n">
-        <v>6394494</v>
+        <v>6394809</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1056,12 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,57 +1071,52 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sandra Johansson, Elin Eriksson</t>
+          <t>Sandra Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129949425</v>
+        <v>129949585</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>99156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>219875</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bollebygd kommun, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>363034</v>
+        <v>362828</v>
       </c>
       <c r="R6" t="n">
-        <v>6394565</v>
+        <v>6394640</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1158,12 +1143,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1183,10 +1168,107 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sandra Johansson, Elin Eriksson</t>
+          <t>Sandra Johansson, Mathias Molau</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>90903850</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Erikshult, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>363091</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6394422</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-08-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-08-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50084-2025 artfynd.xlsx
+++ b/artfynd/A 50084-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129949425</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129949426</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129949383</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129949593</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129949585</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1269,8 +1299,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90903850</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>